--- a/docs/api-to-database-mapping.xlsx
+++ b/docs/api-to-database-mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashleyvance/Documents/Hostinger/USAJOBS Explorer/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71EB482D-D907-CB49-AF8A-A59264AF2485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471ACF97-F70D-2B4C-9CA5-15D611486309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-41480" yWindow="580" windowWidth="27640" windowHeight="16940" xr2:uid="{69320A13-70F9-FE45-9F42-9A9DD36D1DB3}"/>
+    <workbookView xWindow="-48760" yWindow="2920" windowWidth="39120" windowHeight="19120" xr2:uid="{69320A13-70F9-FE45-9F42-9A9DD36D1DB3}"/>
   </bookViews>
   <sheets>
     <sheet name="FieldMap" sheetId="1" r:id="rId1"/>
@@ -1040,7 +1040,7 @@
   <cols>
     <col min="1" max="1" width="23.33203125" style="25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="118.5" style="16" customWidth="1"/>
+    <col min="3" max="3" width="128" style="16" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="49.5" style="16" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="53.5" style="16" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="10.83203125" style="16"/>
@@ -1380,7 +1380,7 @@
         <v>86</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C22" s="18"/>
       <c r="D22" s="19" t="s">
@@ -1395,7 +1395,7 @@
         <v>90</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>92</v>
